--- a/tiflow-core/TMD-3186-vorbereiten-unterlagen-fuer-vorabveroeffentlichung-28-05-2026/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow-core/TMD-3186-vorbereiten-unterlagen-fuer-vorabveroeffentlichung-28-05-2026/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T06:03:55+00:00</t>
+    <t>2026-05-21T06:33:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/TMD-3186-vorbereiten-unterlagen-fuer-vorabveroeffentlichung-28-05-2026/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow-core/TMD-3186-vorbereiten-unterlagen-fuer-vorabveroeffentlichung-28-05-2026/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T06:33:50+00:00</t>
+    <t>2026-05-21T08:07:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-core/TMD-3186-vorbereiten-unterlagen-fuer-vorabveroeffentlichung-28-05-2026/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
+++ b/tiflow-core/TMD-3186-vorbereiten-unterlagen-fuer-vorabveroeffentlichung-28-05-2026/2.0.0-ballot.1/StructureDefinition-ti-feature-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T08:07:57+00:00</t>
+    <t>2026-05-21T09:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
